--- a/data/tqm_answers.xlsx
+++ b/data/tqm_answers.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:Z63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,6 +551,16 @@
           <t>prompt_hash</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>answer_type</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>answer_type_valid</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -650,6 +660,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -749,6 +767,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -848,6 +874,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -947,6 +981,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1046,6 +1088,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1121,7 +1171,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>No distinct art game phase was observed; the class moved from warm-up to art gym.</t>
@@ -1141,6 +1190,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1240,6 +1297,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1339,6 +1404,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1414,7 +1487,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>No art game was conducted.</t>
@@ -1434,6 +1506,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1533,6 +1613,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1608,7 +1696,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>No art game was conducted.</t>
@@ -1628,6 +1715,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1727,6 +1822,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1826,6 +1929,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1925,6 +2036,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2024,6 +2143,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2123,6 +2250,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2222,6 +2357,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2321,6 +2464,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2420,6 +2571,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2519,6 +2678,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2618,6 +2785,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2717,6 +2892,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2792,7 +2975,6 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
           <t>The two girls remain seated and focused on the tasks for the vast majority of the structured time.</t>
@@ -2812,6 +2994,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2911,6 +3101,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3010,6 +3208,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3109,6 +3315,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3208,6 +3422,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3307,6 +3529,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3406,6 +3636,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3481,7 +3719,6 @@
           <t>high</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
           <t>Throughout the session, she speaks softly and praises their work.</t>
@@ -3501,6 +3738,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3576,7 +3821,6 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
           <t>Children work independently on their own collages, though they sit together.</t>
@@ -3596,6 +3840,14 @@
           <t>seed-2026-06-04-shapeA</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3700,6 +3952,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3804,6 +4064,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3908,6 +4176,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4012,6 +4288,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z36" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4116,6 +4400,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4220,6 +4512,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4324,6 +4624,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4428,6 +4736,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4532,6 +4848,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4636,6 +4960,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4740,6 +5072,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z43" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4844,6 +5184,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4948,6 +5296,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5052,6 +5408,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5156,6 +5520,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5260,6 +5632,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5364,6 +5744,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5468,6 +5856,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5572,6 +5968,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z51" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5676,6 +6080,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5780,6 +6192,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5884,6 +6304,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5988,6 +6416,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6092,6 +6528,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6196,6 +6640,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6300,6 +6752,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6404,6 +6864,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z59" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6508,6 +6976,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6612,6 +7088,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6716,6 +7200,14 @@
           <t>seed-2026-06-04-shapeB</t>
         </is>
       </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z62" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6819,6 +7311,14 @@
         <is>
           <t>seed-2026-06-04-shapeB</t>
         </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>free_text</t>
+        </is>
+      </c>
+      <c r="Z63" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6832,7 +7332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6954,6 +7454,16 @@
       <c r="X1" s="1" t="inlineStr">
         <is>
           <t>prompt_hash</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>answer_type</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>answer_type_valid</t>
         </is>
       </c>
     </row>
@@ -6968,7 +7478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7090,6 +7600,16 @@
       <c r="X1" s="1" t="inlineStr">
         <is>
           <t>prompt_hash</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>answer_type</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>answer_type_valid</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7871,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -7387,7 +7906,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -7423,7 +7941,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -7473,7 +7990,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -7502,7 +8018,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -7510,7 +8025,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
